--- a/data/trans_orig/P6715-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6715-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen sentido sus tareas del trabajo en 2012</t>
+          <t>Población según si tienen sentido sus tareas del trabajo en 2012 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,97 +731,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4834</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>947</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5701</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4771</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>11255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13895</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20448</t>
+          <t>19412</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17845</t>
+          <t>17412</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38017</t>
+          <t>37630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16249</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33673</t>
+          <t>34147</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36910</t>
+          <t>37641</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62296</t>
+          <t>66075</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24578</t>
+          <t>24479</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45785</t>
+          <t>46488</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34254</t>
+          <t>32637</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44784</t>
+          <t>44681</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73022</t>
+          <t>74761</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>105472</t>
+          <t>107199</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>131891</t>
+          <t>133101</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73720</t>
+          <t>73991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97110</t>
+          <t>97795</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>187620</t>
+          <t>185398</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>222060</t>
+          <t>221675</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,42%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21346</t>
+          <t>20880</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22595</t>
+          <t>22600</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37760</t>
+          <t>37837</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87491</t>
+          <t>87676</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>124743</t>
+          <t>127785</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83506</t>
+          <t>82457</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>119938</t>
+          <t>122276</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>180055</t>
+          <t>179345</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236266</t>
+          <t>236390</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>202357</t>
+          <t>202479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>254842</t>
+          <t>254602</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121341</t>
+          <t>123701</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162677</t>
+          <t>163489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>336825</t>
+          <t>336809</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>404569</t>
+          <t>405759</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>537416</t>
+          <t>535995</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>596186</t>
+          <t>597482</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>281967</t>
+          <t>284561</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>332190</t>
+          <t>332996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>838420</t>
+          <t>837540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>918776</t>
+          <t>912101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,37%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8719</t>
+          <t>8516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12487</t>
+          <t>13634</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19753</t>
+          <t>21111</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43367</t>
+          <t>44131</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27385</t>
+          <t>26663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33721</t>
+          <t>35067</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63401</t>
+          <t>63790</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38153</t>
+          <t>37916</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66352</t>
+          <t>63950</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37225</t>
+          <t>38073</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65198</t>
+          <t>65791</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>82233</t>
+          <t>81781</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>120647</t>
+          <t>121230</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208658</t>
+          <t>209396</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243190</t>
+          <t>244735</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>149296</t>
+          <t>147950</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>179200</t>
+          <t>178245</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>366567</t>
+          <t>367808</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>414340</t>
+          <t>414476</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,46%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13456</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12798</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32759</t>
+          <t>33738</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13482</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31760</t>
+          <t>32046</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>31870</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56382</t>
+          <t>58937</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>139619</t>
+          <t>139629</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>187783</t>
+          <t>186715</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>120875</t>
+          <t>119180</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>166958</t>
+          <t>164927</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>269812</t>
+          <t>268179</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>336765</t>
+          <t>340977</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>281262</t>
+          <t>284385</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>346831</t>
+          <t>346304</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>190112</t>
+          <t>188356</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>241848</t>
+          <t>244138</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>487930</t>
+          <t>485910</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>570653</t>
+          <t>571646</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>875212</t>
+          <t>877036</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>946736</t>
+          <t>946825</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>526694</t>
+          <t>526248</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>592361</t>
+          <t>589945</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1423612</t>
+          <t>1421222</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1518136</t>
+          <t>1522606</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen sentido sus tareas del trabajo en 2016</t>
+          <t>Población según si tienen sentido sus tareas del trabajo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>11820</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>12179</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13278</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27526</t>
+          <t>28250</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50052</t>
+          <t>50696</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23246</t>
+          <t>23309</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40571</t>
+          <t>41947</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67046</t>
+          <t>68346</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>23084</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44914</t>
+          <t>44195</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31405</t>
+          <t>30897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44708</t>
+          <t>44289</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70442</t>
+          <t>70580</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51593</t>
+          <t>51376</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76988</t>
+          <t>74535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21726</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38279</t>
+          <t>38869</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78621</t>
+          <t>77785</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108099</t>
+          <t>106982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,71%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25533</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21018</t>
+          <t>21283</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18270</t>
+          <t>17971</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39976</t>
+          <t>38632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24858</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49338</t>
+          <t>48790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18787</t>
+          <t>18430</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39173</t>
+          <t>39260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48769</t>
+          <t>48221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80234</t>
+          <t>80438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>116846</t>
+          <t>116838</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>161944</t>
+          <t>160716</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>98271</t>
+          <t>97387</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137210</t>
+          <t>135994</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>224001</t>
+          <t>225780</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>282103</t>
+          <t>284016</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>264881</t>
+          <t>264935</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>321894</t>
+          <t>321756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175844</t>
+          <t>174682</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>222422</t>
+          <t>222369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>457152</t>
+          <t>461046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>530482</t>
+          <t>531195</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,66%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>414233</t>
+          <t>411998</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>473323</t>
+          <t>475223</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>275147</t>
+          <t>275728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>325646</t>
+          <t>326443</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>698625</t>
+          <t>705071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>783083</t>
+          <t>783830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,67%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>913</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>10079</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>14932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25778</t>
+          <t>26176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>11753</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>12512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32827</t>
+          <t>32930</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>25936</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54005</t>
+          <t>51594</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19969</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40664</t>
+          <t>40737</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53388</t>
+          <t>50769</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85071</t>
+          <t>84348</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59731</t>
+          <t>58234</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92034</t>
+          <t>92053</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51638</t>
+          <t>50703</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79559</t>
+          <t>80115</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>119446</t>
+          <t>120106</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>162699</t>
+          <t>163678</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>201540</t>
+          <t>200948</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239376</t>
+          <t>238860</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>189429</t>
+          <t>188325</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>221504</t>
+          <t>222062</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>398460</t>
+          <t>399415</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>447407</t>
+          <t>451098</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>68,45%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14720</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35450</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26119</t>
+          <t>26394</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27761</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53562</t>
+          <t>54879</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41384</t>
+          <t>42245</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71584</t>
+          <t>73507</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>25529</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49206</t>
+          <t>50038</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>72868</t>
+          <t>73715</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>112442</t>
+          <t>110656</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>183307</t>
+          <t>185841</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>239346</t>
+          <t>244570</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>136418</t>
+          <t>139734</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>184135</t>
+          <t>185325</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>336109</t>
+          <t>337019</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>411138</t>
+          <t>409410</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>366202</t>
+          <t>373029</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>435971</t>
+          <t>441015</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>257560</t>
+          <t>256348</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>314171</t>
+          <t>315504</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>644048</t>
+          <t>645112</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>735344</t>
+          <t>729511</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,75%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>685910</t>
+          <t>684091</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>765656</t>
+          <t>761514</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>502846</t>
+          <t>502791</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>566145</t>
+          <t>567275</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1211179</t>
+          <t>1210986</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1309555</t>
+          <t>1312336</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6715-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6715-Estudios-trans_orig.xlsx
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12767</t>
+          <t>14652</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>19513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17412</t>
+          <t>17854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37630</t>
+          <t>37072</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16197</t>
+          <t>15862</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34147</t>
+          <t>33974</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37641</t>
+          <t>36915</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>66075</t>
+          <t>63425</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24479</t>
+          <t>23837</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46488</t>
+          <t>46572</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32637</t>
+          <t>32887</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44681</t>
+          <t>43231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74761</t>
+          <t>72656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>107199</t>
+          <t>105256</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133101</t>
+          <t>131251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73991</t>
+          <t>73539</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97795</t>
+          <t>97282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185398</t>
+          <t>187784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>221675</t>
+          <t>223915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>14785</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>21428</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22600</t>
+          <t>21576</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37837</t>
+          <t>37536</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87676</t>
+          <t>85431</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>127785</t>
+          <t>124303</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82457</t>
+          <t>82804</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>122276</t>
+          <t>122723</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>179345</t>
+          <t>178801</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236390</t>
+          <t>235427</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>202479</t>
+          <t>203896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>254602</t>
+          <t>255736</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>123701</t>
+          <t>123442</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>163489</t>
+          <t>164156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>336809</t>
+          <t>338123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>405759</t>
+          <t>408879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>535995</t>
+          <t>536621</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>597482</t>
+          <t>597575</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>284561</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>332996</t>
+          <t>335698</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>837540</t>
+          <t>834342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>912101</t>
+          <t>912437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,39%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13634</t>
+          <t>13526</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21111</t>
+          <t>20714</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44131</t>
+          <t>45165</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26663</t>
+          <t>25163</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35067</t>
+          <t>34952</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63790</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37916</t>
+          <t>37465</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63950</t>
+          <t>66463</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38073</t>
+          <t>38627</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65791</t>
+          <t>65861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81781</t>
+          <t>82495</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121230</t>
+          <t>120666</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>209396</t>
+          <t>207138</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244735</t>
+          <t>242946</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>147950</t>
+          <t>147819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>178245</t>
+          <t>178196</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>367808</t>
+          <t>366731</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>414476</t>
+          <t>414017</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,38%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13256</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22381</t>
+          <t>20638</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13564</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33738</t>
+          <t>32605</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>12989</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32046</t>
+          <t>31406</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>31952</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58937</t>
+          <t>59330</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>139629</t>
+          <t>139576</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>186715</t>
+          <t>188472</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>119180</t>
+          <t>119598</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>164927</t>
+          <t>166398</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>268179</t>
+          <t>272017</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>340977</t>
+          <t>339031</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>284385</t>
+          <t>282756</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>346304</t>
+          <t>345674</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>188356</t>
+          <t>191755</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>244138</t>
+          <t>244425</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>485910</t>
+          <t>489731</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>571646</t>
+          <t>569674</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>877036</t>
+          <t>875085</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>946825</t>
+          <t>947153</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>526248</t>
+          <t>526633</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>589945</t>
+          <t>588632</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1421222</t>
+          <t>1418805</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1522606</t>
+          <t>1518964</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,38%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11820</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12179</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>27930</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50696</t>
+          <t>50182</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23309</t>
+          <t>23054</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41947</t>
+          <t>41378</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68346</t>
+          <t>66357</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23084</t>
+          <t>23185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44195</t>
+          <t>44077</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>31065</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44289</t>
+          <t>45184</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70580</t>
+          <t>70770</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51376</t>
+          <t>50655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74535</t>
+          <t>75081</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>21919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38869</t>
+          <t>38140</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77785</t>
+          <t>78995</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106982</t>
+          <t>107266</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,84%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8565</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24123</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21283</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17971</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38632</t>
+          <t>39505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24950</t>
+          <t>24904</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48790</t>
+          <t>48856</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18430</t>
+          <t>18779</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39260</t>
+          <t>41119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48221</t>
+          <t>50082</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80438</t>
+          <t>79852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>116838</t>
+          <t>116929</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>160716</t>
+          <t>159550</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>97387</t>
+          <t>96715</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135994</t>
+          <t>137628</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>225780</t>
+          <t>220402</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>284016</t>
+          <t>281262</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>264935</t>
+          <t>265686</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>321756</t>
+          <t>323851</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>174682</t>
+          <t>176387</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>222369</t>
+          <t>222542</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>461046</t>
+          <t>455059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>531195</t>
+          <t>529648</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>411998</t>
+          <t>414566</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>475223</t>
+          <t>473634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>275728</t>
+          <t>274866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>326443</t>
+          <t>326475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>705071</t>
+          <t>706326</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>783830</t>
+          <t>787778</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14932</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26176</t>
+          <t>26542</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32930</t>
+          <t>33380</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25936</t>
+          <t>26786</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51594</t>
+          <t>54674</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>19347</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40737</t>
+          <t>39073</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50769</t>
+          <t>51675</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84348</t>
+          <t>84937</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58234</t>
+          <t>60258</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92053</t>
+          <t>90747</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50703</t>
+          <t>51841</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80115</t>
+          <t>80477</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>120106</t>
+          <t>120119</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>163678</t>
+          <t>161777</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200948</t>
+          <t>200345</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238860</t>
+          <t>235917</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188325</t>
+          <t>188441</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222062</t>
+          <t>219646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>399415</t>
+          <t>400231</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>451098</t>
+          <t>449494</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14559</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>33876</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>10095</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26394</t>
+          <t>26915</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28081</t>
+          <t>28793</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54879</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42245</t>
+          <t>40342</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>70244</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25529</t>
+          <t>24278</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50038</t>
+          <t>49617</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>73715</t>
+          <t>74648</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>110656</t>
+          <t>112447</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>185841</t>
+          <t>186264</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>244570</t>
+          <t>243978</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>139734</t>
+          <t>135691</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>185325</t>
+          <t>181494</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>337019</t>
+          <t>337200</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>409410</t>
+          <t>411836</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>373029</t>
+          <t>370493</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>441015</t>
+          <t>440870</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>256348</t>
+          <t>256759</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>315504</t>
+          <t>312992</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>645112</t>
+          <t>641002</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>729511</t>
+          <t>731383</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>684091</t>
+          <t>687644</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>761514</t>
+          <t>763228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>502791</t>
+          <t>505952</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>567275</t>
+          <t>571772</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1210986</t>
+          <t>1212058</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1312336</t>
+          <t>1309656</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
